--- a/converted_files/837/multi-tran.xlsx
+++ b/converted_files/837/multi-tran.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4ec8</t>
+          <t>69e82c69836d7d05c9a056c1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4ec8</t>
+          <t>69e82c69836d7d05c9a056c1</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2804,7 +2804,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4ec8</t>
+          <t>69e82c69836d7d05c9a056c1</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3189,7 +3189,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4ec8</t>
+          <t>69e82c69836d7d05c9a056c1</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3574,7 +3574,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4ec9</t>
+          <t>69e82c69836d7d05c9a056c2</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -4149,7 +4149,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4eca</t>
+          <t>69e82c69836d7d05c9a056c3</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4758,7 +4758,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4eca</t>
+          <t>69e82c69836d7d05c9a056c3</t>
         </is>
       </c>
       <c r="B8"/>

--- a/converted_files/837/multi-tran.xlsx
+++ b/converted_files/837/multi-tran.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4ec8</t>
+          <t>69efef06ad4799caa7f5e343</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4ec8</t>
+          <t>69efef06ad4799caa7f5e343</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2804,7 +2804,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4ec8</t>
+          <t>69efef06ad4799caa7f5e343</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3189,7 +3189,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4ec8</t>
+          <t>69efef06ad4799caa7f5e343</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3574,7 +3574,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4ec9</t>
+          <t>69efef06ad4799caa7f5e344</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -4149,7 +4149,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4eca</t>
+          <t>69efef06ad4799caa7f5e345</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4758,7 +4758,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4eca</t>
+          <t>69efef06ad4799caa7f5e345</t>
         </is>
       </c>
       <c r="B8"/>

--- a/converted_files/837/multi-tran.xlsx
+++ b/converted_files/837/multi-tran.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a056c1</t>
+          <t>6a04cb3c618f76c4f7b19572</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a056c1</t>
+          <t>6a04cb3c618f76c4f7b19572</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2804,7 +2804,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a056c1</t>
+          <t>6a04cb3c618f76c4f7b19572</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3189,7 +3189,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a056c1</t>
+          <t>6a04cb3c618f76c4f7b19572</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3574,7 +3574,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a056c2</t>
+          <t>6a04cb3c618f76c4f7b19573</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -4149,7 +4149,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a056c3</t>
+          <t>6a04cb3c618f76c4f7b19574</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4758,7 +4758,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a056c3</t>
+          <t>6a04cb3c618f76c4f7b19574</t>
         </is>
       </c>
       <c r="B8"/>

--- a/converted_files/837/multi-tran.xlsx
+++ b/converted_files/837/multi-tran.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b19572</t>
+          <t>6a04cc5c1ef26d534baf4080</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b19572</t>
+          <t>6a04cc5c1ef26d534baf4080</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2804,7 +2804,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b19572</t>
+          <t>6a04cc5c1ef26d534baf4080</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3189,7 +3189,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b19572</t>
+          <t>6a04cc5c1ef26d534baf4080</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3574,7 +3574,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b19573</t>
+          <t>6a04cc5c1ef26d534baf4081</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -4149,7 +4149,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b19574</t>
+          <t>6a04cc5c1ef26d534baf4082</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4758,7 +4758,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b19574</t>
+          <t>6a04cc5c1ef26d534baf4082</t>
         </is>
       </c>
       <c r="B8"/>

--- a/converted_files/837/multi-tran.xlsx
+++ b/converted_files/837/multi-tran.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf4080</t>
+          <t>6a0614def8d6a2fc74348eca</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf4080</t>
+          <t>6a0614def8d6a2fc74348eca</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2804,7 +2804,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf4080</t>
+          <t>6a0614def8d6a2fc74348eca</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3189,7 +3189,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf4080</t>
+          <t>6a0614def8d6a2fc74348eca</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3574,7 +3574,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf4081</t>
+          <t>6a0614def8d6a2fc74348ecb</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -4149,7 +4149,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf4082</t>
+          <t>6a0614def8d6a2fc74348ecc</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4758,7 +4758,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf4082</t>
+          <t>6a0614def8d6a2fc74348ecc</t>
         </is>
       </c>
       <c r="B8"/>

--- a/converted_files/837/multi-tran.xlsx
+++ b/converted_files/837/multi-tran.xlsx
@@ -1832,7 +1832,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348eca</t>
+          <t>6a32cb6497613a0e4990959d</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348eca</t>
+          <t>6a32cb6497613a0e4990959d</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2804,7 +2804,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348eca</t>
+          <t>6a32cb6497613a0e4990959d</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3189,7 +3189,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348eca</t>
+          <t>6a32cb6497613a0e4990959d</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3574,7 +3574,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348ecb</t>
+          <t>6a32cb6497613a0e4990959e</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -4149,7 +4149,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348ecc</t>
+          <t>6a32cb6497613a0e4990959f</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4758,7 +4758,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348ecc</t>
+          <t>6a32cb6497613a0e4990959f</t>
         </is>
       </c>
       <c r="B8"/>
